--- a/exports/ENRIN_full_report.xlsx
+++ b/exports/ENRIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.46</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45877.38541666666</v>
+        <v>45877.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>3103</v>
+        <v>3090</v>
       </c>
       <c r="I2" t="n">
         <v>3091.276813954197</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="L2" t="n">
         <v>3.47</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45889.55208333334</v>
+        <v>45890.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3299.8</v>
+        <v>3370.4</v>
       </c>
       <c r="I3" t="n">
         <v>3354.579204363831</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.79</v>
+        <v>-9.07</v>
       </c>
       <c r="L3" t="n">
-        <v>7.79</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M3" t="n">
         <v>1.43</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.71</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45931.38541666666</v>
+        <v>45931.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>3406.4</v>
+        <v>3396</v>
       </c>
       <c r="I4" t="n">
         <v>3401.075961432534</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.07</v>
+        <v>0.76</v>
       </c>
       <c r="L4" t="n">
         <v>2.68</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>6.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>3194.7</v>
+        <v>3246.8</v>
       </c>
       <c r="I5" t="n">
         <v>3221.174516004446</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>5.93</v>
+        <v>4.39</v>
       </c>
       <c r="L5" t="n">
         <v>1.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="N5" t="n">
         <v>2.1</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>5.54</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>3331.1</v>
+        <v>3175</v>
       </c>
       <c r="I6" t="n">
         <v>3210.872515413038</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>-2.21</v>
       </c>
       <c r="L6" t="n">
-        <v>4.68</v>
+        <v>5.33</v>
       </c>
       <c r="M6" t="n">
         <v>0.55</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.99</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2190</v>
+        <v>2346</v>
       </c>
       <c r="I7" t="n">
         <v>2304.061092086356</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>64</v>
+        <v>64.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>31.02</v>
+        <v>26.11</v>
       </c>
       <c r="L7" t="n">
         <v>5.2</v>
@@ -840,7 +923,7 @@
         <v>2.36</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>7.58</v>
       </c>
       <c r="O7" t="n">
         <v>-4.88</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.14</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2786</v>
+        <v>2720.3</v>
       </c>
       <c r="I8" t="n">
         <v>2773.970649648435</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K8" t="n">
-        <v>18.76</v>
+        <v>15.95</v>
       </c>
       <c r="L8" t="n">
         <v>6.22</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46121.55208333334</v>
+        <v>46122.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2768.7</v>
+        <v>2797.3</v>
       </c>
       <c r="I9" t="n">
         <v>2783.766059028382</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.78</v>
+        <v>-2.83</v>
       </c>
       <c r="L9" t="n">
         <v>6.89</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.3</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>3130.3</v>
+        <v>3067</v>
       </c>
       <c r="I10" t="n">
         <v>3097.704168541261</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>11.9</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>1.24</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.72</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3145</v>
+        <v>3387</v>
       </c>
       <c r="I11" t="n">
         <v>3275.953409635678</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.54</v>
+        <v>-10.43</v>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>10.53</v>
       </c>
       <c r="M11" t="n">
         <v>2.16</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>10.81</v>
       </c>
       <c r="O11" t="n">
         <v>-3</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.81</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>3582</v>
+        <v>3493.1</v>
       </c>
       <c r="I12" t="n">
         <v>3511.829887213577</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>5.76</v>
+        <v>3.13</v>
       </c>
       <c r="L12" t="n">
         <v>7.3</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.74</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3610.1</v>
+        <v>3720.5</v>
       </c>
       <c r="I13" t="n">
         <v>3683.264563711945</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.35</v>
+        <v>-6.51</v>
       </c>
       <c r="L13" t="n">
-        <v>5.56</v>
+        <v>7.63</v>
       </c>
       <c r="M13" t="n">
         <v>1.29</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>9.02</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46204.55208333334</v>
+        <v>46205.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3634.9</v>
+        <v>3519.2</v>
       </c>
       <c r="I14" t="n">
         <v>3573.071319729137</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.3</v>
+        <v>-5.41</v>
       </c>
       <c r="L14" t="n">
-        <v>4.85</v>
+        <v>5.6</v>
       </c>
       <c r="M14" t="n">
         <v>0.64</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.07</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3255.6</v>
+        <v>3683.1</v>
       </c>
       <c r="I15" t="n">
         <v>3323.201327815751</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n">
-        <v>7.49</v>
+        <v>-4.66</v>
       </c>
       <c r="L15" t="n">
-        <v>3.72</v>
+        <v>6.13</v>
       </c>
       <c r="M15" t="n">
-        <v>1.35</v>
+        <v>5.97</v>
       </c>
       <c r="N15" t="n">
-        <v>3.66</v>
+        <v>12.05</v>
       </c>
       <c r="O15" t="n">
         <v>-2.07</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.87</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3390.1</v>
+        <v>3314</v>
       </c>
       <c r="I16" t="n">
         <v>3381.330506970802</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.96</v>
+        <v>-10.02</v>
       </c>
       <c r="L16" t="n">
-        <v>8.470000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="M16" t="n">
         <v>0.33</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46283.38541666666</v>
+        <v>46283.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>3157.5</v>
+        <v>3245</v>
       </c>
       <c r="I17" t="n">
         <v>3208.975284126181</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>4.72</v>
+        <v>2.08</v>
       </c>
       <c r="L17" t="n">
         <v>3.02</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.16</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46303.55208333334</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3187.1</v>
+        <v>3150.2</v>
       </c>
       <c r="I18" t="n">
         <v>3155.755983640737</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.78</v>
+        <v>-2.92</v>
       </c>
       <c r="L18" t="n">
-        <v>3.69</v>
+        <v>6.04</v>
       </c>
       <c r="M18" t="n">
         <v>0.6</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1527,6 +1754,12 @@
       <c r="Q19" t="n">
         <v>24</v>
       </c>
+      <c r="R19" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2235,7 +2468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.9</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="6">
@@ -2245,7 +2478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="7">
@@ -2255,7 +2488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="8">
@@ -2265,7 +2498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="9">
@@ -2275,7 +2508,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -2285,7 +2518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="11">
@@ -2325,7 +2558,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.21</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="15">
@@ -2335,7 +2568,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.09</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="16">
@@ -2345,7 +2578,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.34</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="17">
@@ -2355,7 +2588,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.02</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="18">
@@ -2365,7 +2598,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.8</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="19">
@@ -2375,7 +2608,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.68</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="20">
@@ -2385,7 +2618,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.68</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="21">
@@ -2395,7 +2628,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.470000000000001</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="22">
@@ -2405,7 +2638,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -2415,7 +2648,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2425,7 +2658,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="25">
@@ -2435,7 +2668,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.7</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="26">
@@ -2445,7 +2678,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.5</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="27">
@@ -2455,7 +2688,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.23</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="28">
@@ -2465,7 +2698,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
